--- a/downloads/client-tracker.xlsx
+++ b/downloads/client-tracker.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מעקב לקוחות" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'מעקב לקוחות'!$A$1:$F$1,'מעקב לקוחות'!$A$4:$F$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -474,9 +476,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -710,85 +712,53 @@
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>סיכום</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>סה"כ בסטטוס "ליד"</t>
+        </is>
+      </c>
+      <c r="B13" s="8">
+        <f>COUNTIF(D5:D11,"ליד")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>סה"כ בסטטוס "פעיל"</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <f>COUNTIF(D5:D11,"פעיל")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>סיכום</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>סה"כ בסטטוס "ליד"</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>COUNTIF(D5:D15,"ליד")</f>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>סה"כ בסטטוס "סגור"</t>
+        </is>
+      </c>
+      <c r="B15" s="8">
+        <f>COUNTIF(D5:D11,"סגור")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>סה"כ בסטטוס "פעיל"</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>COUNTIF(D5:D15,"פעיל")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>סה"כ בסטטוס "סגור"</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>COUNTIF(D5:D15,"סגור")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>סה"כ לקוחות</t>
         </is>
       </c>
-      <c r="B21" s="10">
-        <f>COUNTA(A5:A15)</f>
+      <c r="B16" s="10">
+        <f>COUNTA(A5:A11)</f>
         <v/>
       </c>
     </row>
@@ -798,5 +768,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/downloads/client-tracker.xlsx
+++ b/downloads/client-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מעקב לקוחות" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'מעקב לקוחות'!$A$1:$F$1,'מעקב לקוחות'!$A$4:$F$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'מעקב לקוחות'!$A$1:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" hidden="1" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>מלאו את פרטי הלקוחות (התאים הצהובים) — הסיכום למטה מתעדכן אוטומטית</t>
